--- a/plate3d/PLATE3D_TEMPLATE.xlsx
+++ b/plate3d/PLATE3D_TEMPLATE.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="203">
   <si>
     <t># PLATE3D  ·  blank input sheet</t>
   </si>
@@ -110,6 +110,45 @@
   </si>
   <si>
     <t>length</t>
+  </si>
+  <si>
+    <t># BOLT</t>
+  </si>
+  <si>
+    <t>[hole]</t>
+  </si>
+  <si>
+    <t>[head_af]</t>
+  </si>
+  <si>
+    <t>[head_h]</t>
+  </si>
+  <si>
+    <t>[nut_af]</t>
+  </si>
+  <si>
+    <t>[nut_h]</t>
+  </si>
+  <si>
+    <t>[proj]</t>
+  </si>
+  <si>
+    <t>#   A BOLT is a BAR that knows it is one: the engine works out which members its</t>
+  </si>
+  <si>
+    <t>#   axis crosses and puts the hole on their part drawings, so a hole is never typed.</t>
+  </si>
+  <si>
+    <t>#   The point it is placed on is the UNDERSIDE OF THE HEAD - the steel face the bolt</t>
+  </si>
+  <si>
+    <t>#   pulls against. length = grip + nut + proj. Only the first four are needed; the</t>
+  </si>
+  <si>
+    <t>#   rest come off the diameter (hole d+2, across-flats 1.5d, head 0.625d, nut 0.9d,</t>
+  </si>
+  <si>
+    <t>#   proj 0.2d). Turn one round with the ROT columns on its MODULE row.</t>
   </si>
   <si>
     <t># SECT</t>
@@ -1003,7 +1042,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:R149"/>
+  <dimension ref="B1:R159"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="11" customWidth="1"/>
@@ -1194,7 +1233,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B30" s="3" t="s">
         <v>33</v>
       </c>
@@ -1205,832 +1244,839 @@
         <v>18</v>
       </c>
       <c r="E30" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F30" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="F30" s="4" t="s">
-        <v>23</v>
-      </c>
       <c r="G30" s="4" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="M30" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="N30" s="4" t="s">
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B31" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B31" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F31" s="4" t="s">
+    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B32" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="G31" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="I31" s="4" t="s">
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="J31" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="K31" s="4" t="s">
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B34" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="L31" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="M31" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B32" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H32" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="I32" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="J32" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="K32" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="L32" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="M32" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B33" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H33" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="I33" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B34" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H34" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="I34" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="J34" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="K34" s="4" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="35" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B35" s="2" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
     </row>
     <row r="36" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B36" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B37" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B40" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="J40" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="K40" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="L40" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="M40" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="N40" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B41" s="3" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>17</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E41" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G41" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F41" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="H41" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="J41" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="K41" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="L41" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="M41" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B42" s="3" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>17</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E42" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G42" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F42" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G42" s="4" t="s">
-        <v>26</v>
-      </c>
       <c r="H42" s="4" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+      <c r="J42" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K42" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="L42" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="M42" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="43" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B43" s="3" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>17</v>
       </c>
       <c r="D43" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="44" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B44" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="I44" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="J44" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="K44" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B45" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B46" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B47" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="51" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B51" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="52" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B52" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I52" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="53" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B53" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D53" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E43" s="4" t="s">
+      <c r="E53" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F43" s="4" t="s">
+      <c r="F53" s="4" t="s">
         <v>29</v>
-      </c>
-    </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B47" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B48" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B49" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B50" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B51" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="53" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B53" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E53" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="G53" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="H53" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="I53" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="J53" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="K53" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="L53" s="4" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="57" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="58" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B58" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="59" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B59" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="60" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B60" s="2" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="61" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B61" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="63" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B63" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C63" s="4" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="62" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B62" s="3" t="s">
+      <c r="D63" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="C62" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D62" s="4" t="s">
+      <c r="E63" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="E62" s="4" t="s">
+      <c r="F63" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="F62" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="G62" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="H62" s="4" t="s">
+      <c r="G63" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="I62" s="4" t="s">
+      <c r="H63" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="J62" s="4" t="s">
+      <c r="I63" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="K62" s="4" t="s">
+      <c r="J63" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="L62" s="4" t="s">
+      <c r="K63" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="M62" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="N62" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="O62" s="4" t="s">
+      <c r="L63" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="P62" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B66" s="2" t="s">
+    </row>
+    <row r="67" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B67" s="1" t="s">
         <v>89</v>
-      </c>
-    </row>
-    <row r="67" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B67" s="2" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="68" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B68" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B69" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B69" s="3" t="s">
+    <row r="71" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B71" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B72" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="F72" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="C69" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D69" s="4" t="s">
+      <c r="G72" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="E69" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="F69" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="G69" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="H69" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="I69" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="J69" s="4" t="s">
+      <c r="H72" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="K69" s="4" t="s">
+      <c r="I72" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="L69" s="4" t="s">
+      <c r="J72" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="M69" s="4" t="s">
+      <c r="K72" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="N69" s="4" t="s">
+      <c r="L72" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="O69" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="P69" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q69" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="R69" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="73" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B73" s="2" t="s">
+      <c r="M72" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="N72" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="O72" s="4" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="74" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B74" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C74" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D74" s="4" t="s">
+      <c r="P72" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="76" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B76" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="E74" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="F74" s="4" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="77" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B77" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="78" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B78" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B79" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="F79" s="4" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="78" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B78" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C78" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D78" s="4" t="s">
+      <c r="G79" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="E78" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F78" s="4" t="s">
+      <c r="H79" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="G78" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="H78" s="4" t="s">
+      <c r="I79" s="4" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="82" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B82" s="1" t="s">
+      <c r="J79" s="4" t="s">
         <v>109</v>
+      </c>
+      <c r="K79" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="L79" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="M79" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="N79" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="O79" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="P79" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q79" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="R79" s="4" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="83" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B83" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="84" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B84" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="86" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B86" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C86" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="84" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B84" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C84" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D86" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="E86" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="F86" s="4" t="s">
+      <c r="D84" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="G86" s="4" t="s">
+      <c r="E84" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="H86" s="4" t="s">
+      <c r="F84" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="I86" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="J86" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="K86" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="87" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B87" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C87" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D87" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="E87" s="4" t="s">
+    </row>
+    <row r="87" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B87" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="F87" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="G87" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="H87" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="I87" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="88" spans="2:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="88" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B88" s="3" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>17</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>119</v>
+        <v>94</v>
       </c>
       <c r="F88" s="4" t="s">
         <v>120</v>
       </c>
       <c r="G88" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="H88" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="H88" s="4" t="s">
+    </row>
+    <row r="92" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B92" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="I88" s="4" t="s">
+    </row>
+    <row r="93" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B93" s="2" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="89" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B89" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C89" s="4" t="s">
+    <row r="94" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B94" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="96" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B96" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C96" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D89" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="E89" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="F89" s="4" t="s">
+      <c r="D96" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E96" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="G96" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="H96" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="I96" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="J96" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="K96" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="97" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B97" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="G89" s="4" t="s">
+      <c r="C97" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D97" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="H89" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="I89" s="4" t="s">
+      <c r="E97" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="F97" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="J89" s="4" t="s">
+      <c r="G97" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="K89" s="4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="90" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B90" s="2" t="s">
+      <c r="H97" s="4" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="95" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B95" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="96" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B96" s="2" t="s">
+      <c r="I97" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="98" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B98" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E98" s="4" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="98" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B98" s="3" t="s">
+      <c r="F98" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="C98" s="4" t="s">
+      <c r="G98" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="D98" s="4" t="s">
+      <c r="H98" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="E98" s="4" t="s">
+      <c r="I98" s="4" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="99" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B99" s="2" t="s">
+    <row r="99" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B99" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E99" s="4" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="103" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B103" s="5" t="s">
+      <c r="F99" s="4" t="s">
         <v>138</v>
       </c>
+      <c r="G99" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="H99" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="I99" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="J99" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="K99" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="100" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B100" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="105" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B105" s="1" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="106" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B106" s="6" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="107" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B107" s="6"/>
+      <c r="B106" s="2" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="108" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B108" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="E108" s="7" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="109" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B109" s="6"/>
-      <c r="E109" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="F109" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="G109" s="7" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="110" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B110" s="6"/>
-      <c r="E110" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="F110" s="7" t="s">
+      <c r="B108" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="G110" s="7" t="s">
+      <c r="C108" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="H110" s="7" t="s">
+      <c r="D108" s="4" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="111" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B111" s="6"/>
-      <c r="E111" s="7" t="s">
+      <c r="E108" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="F111" s="7" t="s">
+    </row>
+    <row r="109" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B109" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="G111" s="7" t="s">
+    </row>
+    <row r="113" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B113" s="5" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="112" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B112" s="6"/>
-      <c r="E112" s="7" t="s">
+    <row r="116" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B116" s="6" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="113" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B113" s="6"/>
-    </row>
-    <row r="114" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B114" s="6" t="s">
+    <row r="117" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B117" s="6"/>
+    </row>
+    <row r="118" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B118" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="E114" s="7" t="s">
+      <c r="E118" s="7" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="115" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B115" s="6"/>
-      <c r="E115" s="7" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="116" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B116" s="6"/>
-    </row>
-    <row r="117" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B117" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="E117" s="7" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="118" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B118" s="6"/>
-      <c r="E118" s="7" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="119" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B119" s="6"/>
       <c r="E119" s="7" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="120" spans="2:5" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+      <c r="F119" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="G119" s="7" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="120" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B120" s="6"/>
       <c r="E120" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F120" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="G120" s="7" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="121" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="H120" s="7" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="121" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B121" s="6"/>
       <c r="E121" s="7" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="122" spans="2:2" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+      <c r="F121" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="G121" s="7" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="122" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B122" s="6"/>
-    </row>
-    <row r="123" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B123" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="E123" s="7" t="s">
-        <v>163</v>
-      </c>
+      <c r="E122" s="7" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="123" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B123" s="6"/>
     </row>
     <row r="124" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B124" s="6"/>
+      <c r="B124" s="6" t="s">
+        <v>166</v>
+      </c>
       <c r="E124" s="7" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="125" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B125" s="6"/>
       <c r="E125" s="7" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="126" spans="2:5" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="126" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B126" s="6"/>
-      <c r="E126" s="7" t="s">
-        <v>166</v>
-      </c>
     </row>
     <row r="127" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B127" s="6"/>
+      <c r="B127" s="6" t="s">
+        <v>169</v>
+      </c>
       <c r="E127" s="7" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="128" spans="2:2" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="128" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B128" s="6"/>
+      <c r="E128" s="7" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="129" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B129" s="6" t="s">
-        <v>168</v>
-      </c>
+      <c r="B129" s="6"/>
       <c r="E129" s="7" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="130" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B130" s="6"/>
       <c r="E130" s="7" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="131" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B131" s="6"/>
       <c r="E131" s="7" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="132" spans="2:2" x14ac:dyDescent="0.25">
@@ -2038,56 +2084,57 @@
     </row>
     <row r="133" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B133" s="6" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E133" s="7" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="134" spans="2:2" x14ac:dyDescent="0.25">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="134" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B134" s="6"/>
+      <c r="E134" s="7" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="135" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B135" s="6" t="s">
-        <v>174</v>
-      </c>
+      <c r="B135" s="6"/>
       <c r="E135" s="7" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="136" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B136" s="6"/>
       <c r="E136" s="7" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="137" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B137" s="6"/>
       <c r="E137" s="7" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="138" spans="2:5" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="138" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B138" s="6"/>
-      <c r="E138" s="7" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="139" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B139" s="6"/>
+    </row>
+    <row r="139" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B139" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="E139" s="7" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="140" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B140" s="6" t="s">
-        <v>179</v>
-      </c>
+      <c r="B140" s="6"/>
       <c r="E140" s="7" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="141" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B141" s="6"/>
       <c r="E141" s="7" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="142" spans="2:2" x14ac:dyDescent="0.25">
@@ -2095,10 +2142,10 @@
     </row>
     <row r="143" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B143" s="6" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E143" s="7" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="144" spans="2:2" x14ac:dyDescent="0.25">
@@ -2106,33 +2153,90 @@
     </row>
     <row r="145" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B145" s="6" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E145" s="7" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="146" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B146" s="6"/>
       <c r="E146" s="7" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="147" spans="2:2" x14ac:dyDescent="0.25">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="147" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B147" s="6"/>
+      <c r="E147" s="7" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="148" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B148" s="6" t="s">
-        <v>187</v>
-      </c>
+      <c r="B148" s="6"/>
       <c r="E148" s="7" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="149" spans="2:5" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="149" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B149" s="6"/>
-      <c r="E149" s="7" t="s">
-        <v>189</v>
+    </row>
+    <row r="150" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B150" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="E150" s="7" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="151" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B151" s="6"/>
+      <c r="E151" s="7" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="152" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B152" s="6"/>
+    </row>
+    <row r="153" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B153" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="E153" s="7" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="154" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B154" s="6"/>
+    </row>
+    <row r="155" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B155" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="E155" s="7" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="156" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B156" s="6"/>
+      <c r="E156" s="7" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="157" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B157" s="6"/>
+    </row>
+    <row r="158" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B158" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="E158" s="7" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="159" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B159" s="6"/>
+      <c r="E159" s="7" t="s">
+        <v>202</v>
       </c>
     </row>
   </sheetData>

--- a/plate3d/PLATE3D_TEMPLATE.xlsx
+++ b/plate3d/PLATE3D_TEMPLATE.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="199">
   <si>
     <t># PLATE3D  ·  blank input sheet</t>
   </si>
@@ -367,18 +367,6 @@
     <t>point</t>
   </si>
   <si>
-    <t>#   cut one end of a member to the face it runs into. B = start, E = end.</t>
-  </si>
-  <si>
-    <t>FIT</t>
-  </si>
-  <si>
-    <t>B / E</t>
-  </si>
-  <si>
-    <t>[GAP]</t>
-  </si>
-  <si>
     <t># 4.  ASSY  ·  modules, plates and bars into the world</t>
   </si>
   <si>
@@ -583,7 +571,7 @@
     <t>Name the same part as often as you use it - the engine numbers the repeats</t>
   </si>
   <si>
-    <t>itself, pl.stf twice becoming pl.stf_1 and pl.stf_2. A BASE or a FIT row</t>
+    <t>itself, pl.stf twice becoming pl.stf_1 and pl.stf_2. A BASE row</t>
   </si>
   <si>
     <t>wants the numbered name.</t>
@@ -1042,7 +1030,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:R159"/>
+  <dimension ref="B1:R154"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="11" customWidth="1"/>
@@ -1769,383 +1757,384 @@
       </c>
     </row>
     <row r="87" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B87" s="2" t="s">
+      <c r="B87" s="1" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B88" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C88" s="4" t="s">
+    <row r="88" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B88" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="89" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B89" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="91" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B91" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C91" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D88" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="E88" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="F88" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="G88" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="H88" s="4" t="s">
+      <c r="D91" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="G91" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="H91" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="I91" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="J91" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="K91" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="92" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B92" s="3" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="92" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B92" s="1" t="s">
+      <c r="C92" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D92" s="4" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="93" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B93" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="94" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B94" s="2" t="s">
+      <c r="E92" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="F92" s="4" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="96" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B96" s="3" t="s">
+      <c r="G92" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="C96" s="4" t="s">
+      <c r="H92" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="I92" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="93" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B93" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C93" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D96" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E96" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="F96" s="4" t="s">
+      <c r="D93" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E93" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="G96" s="4" t="s">
+      <c r="F93" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="H96" s="4" t="s">
+      <c r="G93" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="I96" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="J96" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="K96" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="97" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B97" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C97" s="4" t="s">
+      <c r="H93" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="I93" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="94" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B94" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C94" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D97" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E97" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="F97" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="G97" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="H97" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="I97" s="4" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="98" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B98" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C98" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D98" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E98" s="4" t="s">
+      <c r="D94" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E94" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="G94" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="H94" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="I94" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J94" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="K94" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="F98" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="G98" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="H98" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="I98" s="4" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="99" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B99" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C99" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D99" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E99" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="F99" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="G99" s="4" t="s">
+    </row>
+    <row r="95" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B95" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="H99" s="4" t="s">
+    </row>
+    <row r="100" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B100" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="I99" s="4" t="s">
+    </row>
+    <row r="101" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B101" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="J99" s="4" t="s">
+    </row>
+    <row r="103" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B103" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="K99" s="4" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="100" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B100" s="2" t="s">
+      <c r="C103" s="4" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="105" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B105" s="1" t="s">
+      <c r="D103" s="4" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="106" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B106" s="2" t="s">
+      <c r="E103" s="4" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="108" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B108" s="3" t="s">
+    <row r="104" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B104" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C108" s="4" t="s">
+    </row>
+    <row r="108" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B108" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="D108" s="4" t="s">
+    </row>
+    <row r="111" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B111" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="E108" s="4" t="s">
+    </row>
+    <row r="112" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B112" s="6"/>
+    </row>
+    <row r="113" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B113" s="6" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="109" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B109" s="2" t="s">
+      <c r="E113" s="7" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="113" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B113" s="5" t="s">
+    <row r="114" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B114" s="6"/>
+      <c r="E114" s="7" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="116" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B116" s="6" t="s">
+      <c r="F114" s="7" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="117" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="G114" s="7" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="115" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B115" s="6"/>
+      <c r="E115" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="F115" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="G115" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H115" s="7" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="116" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B116" s="6"/>
+      <c r="E116" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F116" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="G116" s="7" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="117" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B117" s="6"/>
-    </row>
-    <row r="118" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B118" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E118" s="7" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="119" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B119" s="6"/>
+      <c r="E117" s="7" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="118" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B118" s="6"/>
+    </row>
+    <row r="119" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B119" s="6" t="s">
+        <v>162</v>
+      </c>
       <c r="E119" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="F119" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="G119" s="7" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="120" spans="2:8" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="120" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B120" s="6"/>
       <c r="E120" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="F120" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="G120" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="H120" s="7" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="121" spans="2:7" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="121" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B121" s="6"/>
-      <c r="E121" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="F121" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="G121" s="7" t="s">
-        <v>164</v>
-      </c>
     </row>
     <row r="122" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B122" s="6"/>
+      <c r="B122" s="6" t="s">
+        <v>165</v>
+      </c>
       <c r="E122" s="7" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="123" spans="2:2" x14ac:dyDescent="0.25">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="123" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B123" s="6"/>
+      <c r="E123" s="7" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="124" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B124" s="6" t="s">
-        <v>166</v>
-      </c>
+      <c r="B124" s="6"/>
       <c r="E124" s="7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="125" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B125" s="6"/>
       <c r="E125" s="7" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="126" spans="2:2" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="126" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B126" s="6"/>
-    </row>
-    <row r="127" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B127" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="E127" s="7" t="s">
+      <c r="E126" s="7" t="s">
         <v>170</v>
       </c>
     </row>
+    <row r="127" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B127" s="6"/>
+    </row>
     <row r="128" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B128" s="6"/>
+      <c r="B128" s="6" t="s">
+        <v>171</v>
+      </c>
       <c r="E128" s="7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="129" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B129" s="6"/>
       <c r="E129" s="7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="130" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B130" s="6"/>
       <c r="E130" s="7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="131" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B131" s="6"/>
       <c r="E131" s="7" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="132" spans="2:2" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="132" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B132" s="6"/>
-    </row>
-    <row r="133" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B133" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="E133" s="7" t="s">
+      <c r="E132" s="7" t="s">
         <v>176</v>
       </c>
     </row>
+    <row r="133" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B133" s="6"/>
+    </row>
     <row r="134" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B134" s="6"/>
+      <c r="B134" s="6" t="s">
+        <v>177</v>
+      </c>
       <c r="E134" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="135" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B135" s="6"/>
       <c r="E135" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="136" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B136" s="6"/>
       <c r="E136" s="7" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="137" spans="2:5" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="137" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B137" s="6"/>
-      <c r="E137" s="7" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="138" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B138" s="6"/>
-    </row>
-    <row r="139" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B139" s="6" t="s">
+    </row>
+    <row r="138" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B138" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="E139" s="7" t="s">
+      <c r="E138" s="7" t="s">
         <v>182</v>
       </c>
     </row>
+    <row r="139" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B139" s="6"/>
+    </row>
     <row r="140" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B140" s="6"/>
+      <c r="B140" s="6" t="s">
+        <v>183</v>
+      </c>
       <c r="E140" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="141" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B141" s="6"/>
       <c r="E141" s="7" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="142" spans="2:2" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="142" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B142" s="6"/>
+      <c r="E142" s="7" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="143" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B143" s="6" t="s">
-        <v>185</v>
-      </c>
+      <c r="B143" s="6"/>
       <c r="E143" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="144" spans="2:2" x14ac:dyDescent="0.25">
@@ -2153,28 +2142,27 @@
     </row>
     <row r="145" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B145" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E145" s="7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="146" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B146" s="6"/>
       <c r="E146" s="7" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="147" spans="2:5" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="147" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B147" s="6"/>
-      <c r="E147" s="7" t="s">
-        <v>190</v>
-      </c>
     </row>
     <row r="148" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B148" s="6"/>
+      <c r="B148" s="6" t="s">
+        <v>191</v>
+      </c>
       <c r="E148" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="149" spans="2:2" x14ac:dyDescent="0.25">
@@ -2182,16 +2170,16 @@
     </row>
     <row r="150" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B150" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E150" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="151" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B151" s="6"/>
       <c r="E151" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="152" spans="2:2" x14ac:dyDescent="0.25">
@@ -2199,44 +2187,16 @@
     </row>
     <row r="153" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B153" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E153" s="7" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="154" spans="2:2" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="154" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B154" s="6"/>
-    </row>
-    <row r="155" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B155" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="E155" s="7" t="s">
+      <c r="E154" s="7" t="s">
         <v>198</v>
-      </c>
-    </row>
-    <row r="156" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B156" s="6"/>
-      <c r="E156" s="7" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="157" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B157" s="6"/>
-    </row>
-    <row r="158" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B158" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="E158" s="7" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="159" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B159" s="6"/>
-      <c r="E159" s="7" t="s">
-        <v>202</v>
       </c>
     </row>
   </sheetData>

--- a/plate3d/PLATE3D_TEMPLATE.xlsx
+++ b/plate3d/PLATE3D_TEMPLATE.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="261">
   <si>
     <t># PLATE3D  ·  blank input sheet</t>
   </si>
@@ -229,6 +229,63 @@
     <t>#   corner - the inner one is r minus the wall and is not asked for.</t>
   </si>
   <si>
+    <t># TAPER</t>
+  </si>
+  <si>
+    <t>begin</t>
+  </si>
+  <si>
+    <t>end</t>
+  </si>
+  <si>
+    <t>beg.pt</t>
+  </si>
+  <si>
+    <t>end.pt</t>
+  </si>
+  <si>
+    <t>taper.pt</t>
+  </si>
+  <si>
+    <t>Length</t>
+  </si>
+  <si>
+    <t>#   A member whose section changes along its length. This row does not MODIFY a</t>
+  </si>
+  <si>
+    <t>#   member, it MAKES one: it names two SECT rows written above and builds a single</t>
+  </si>
+  <si>
+    <t>#   member flowing between them, under a new id that MODULE and ASSY call like any</t>
+  </si>
+  <si>
+    <t>#   other. The two sections are shapes only - their own length and base.pt are not</t>
+  </si>
+  <si>
+    <t>#   used; the Length on this row is.</t>
+  </si>
+  <si>
+    <t>#   Both must be the same shape - H to H, R to R. A tube into a solid is refused,</t>
+  </si>
+  <si>
+    <t>#   and so is a different number of corners.</t>
+  </si>
+  <si>
+    <t>#   beg.pt / end.pt are SHAPE: which of the nine points of the two sections lie on</t>
+  </si>
+  <si>
+    <t>#   one axis. mc to mc is concentric; bc to bc keeps one flat face.</t>
+  </si>
+  <si>
+    <t>#   taper.pt is PLACEMENT: the point the MODULE row grips, on the START section.</t>
+  </si>
+  <si>
+    <t>#   A member that is prismatic for part of its length is written as two members.</t>
+  </si>
+  <si>
+    <t>#   CUT and NOTCH cannot be aimed at a tapered member.</t>
+  </si>
+  <si>
     <t># HOLE</t>
   </si>
   <si>
@@ -280,6 +337,54 @@
     <t>[repeat2]</t>
   </si>
   <si>
+    <t>#   NOTCH is CUT with two more columns, and they are the whole difference. A CUT</t>
+  </si>
+  <si>
+    <t>#   on a section takes the shape out of the WHOLE length, because a profile has no</t>
+  </si>
+  <si>
+    <t>#   length; from / to say which stretch of the member instead. Both are distances</t>
+  </si>
+  <si>
+    <t>#   along the member from its start.</t>
+  </si>
+  <si>
+    <t># NOTCH</t>
+  </si>
+  <si>
+    <t>member</t>
+  </si>
+  <si>
+    <t>from</t>
+  </si>
+  <si>
+    <t>to</t>
+  </si>
+  <si>
+    <t>#   Or name another member as the knife and let the engine work out the shape it</t>
+  </si>
+  <si>
+    <t>#   leaves. The word BY is not optional - both cells hold member names, and</t>
+  </si>
+  <si>
+    <t>#   without it only the order says which one does the cutting.</t>
+  </si>
+  <si>
+    <t>BY</t>
+  </si>
+  <si>
+    <t>[clearance]</t>
+  </si>
+  <si>
+    <t>#   BY takes a PLATE. A section is refused: the mark a section leaves changes as</t>
+  </si>
+  <si>
+    <t>#   you go into it - 300 of flange, then 10 of web - and a cut that changes along</t>
+  </si>
+  <si>
+    <t>#   the way is not a notch. Cut by a section with the form above.</t>
+  </si>
+  <si>
     <t># 3.  MODULE  ·  where each member sits inside one module</t>
   </si>
   <si>
@@ -295,9 +400,6 @@
     <t># MODULE</t>
   </si>
   <si>
-    <t>member</t>
-  </si>
-  <si>
     <t>Ref.Pt</t>
   </si>
   <si>
@@ -367,6 +469,24 @@
     <t>point</t>
   </si>
   <si>
+    <t>#   a plate carried on one of this module’s own planes - a stiffener, a cover,</t>
+  </si>
+  <si>
+    <t>#   a base plate. L.X / L.Y are on that plane; OFFSET lifts it off the plane.</t>
+  </si>
+  <si>
+    <t>POS</t>
+  </si>
+  <si>
+    <t>plate</t>
+  </si>
+  <si>
+    <t>[ROT]</t>
+  </si>
+  <si>
+    <t>[OFFSET]</t>
+  </si>
+  <si>
     <t># 4.  ASSY  ·  modules, plates and bars into the world</t>
   </si>
   <si>
@@ -433,10 +553,10 @@
     <t>#   repeat = EXTRA copies. repeat 4 leaves five in total.</t>
   </si>
   <si>
-    <t># 5.  VIEW  ·  named drawings for Save DXF   (optional)</t>
-  </si>
-  <si>
-    <t>#   No VIEW rows means no VIEWS block in the DXF. Nothing else changes.</t>
+    <t># 5.  DRAWINGS  ·  what Save DXF puts in the file   (optional)</t>
+  </si>
+  <si>
+    <t>#   No VIEW and no PLOT rows means no drawings in the DXF. Nothing else changes.</t>
   </si>
   <si>
     <t># VIEW</t>
@@ -445,13 +565,79 @@
     <t>module</t>
   </si>
   <si>
-    <t>FROM</t>
+    <t>dir</t>
+  </si>
+  <si>
+    <t>[AZ]</t>
+  </si>
+  <si>
+    <t>[EL]</t>
+  </si>
+  <si>
+    <t>scale</t>
   </si>
   <si>
     <t>[title]</t>
   </si>
   <si>
-    <t>#   FROM = FRONT / BACK / LEFT / RIGHT / TOP / BOTTOM</t>
+    <t>#   module = a MODULE id, an ASSY id, or ALL - the whole model in one drawing.</t>
+  </si>
+  <si>
+    <t>#   dir = FRONT / BACK / LEFT / RIGHT / TOP / BOTTOM</t>
+  </si>
+  <si>
+    <t>#         ISO-NE / ISO-NW / ISO-SE / ISO-SW   (ISO_NE and "ISO NE" also read)</t>
+  </si>
+  <si>
+    <t>#         3D - and then AZ and EL are yours to fill in.</t>
+  </si>
+  <si>
+    <t>#   A named direction leaves AZ and EL EMPTY rather than sliding the scale two</t>
+  </si>
+  <si>
+    <t>#   cells left. The columns do not move.</t>
+  </si>
+  <si>
+    <t>#   LEFT and RIGHT look ALONG the model, which is the only way a section can be</t>
+  </si>
+  <si>
+    <t>#   taken - and a module placed many times lands on top of itself there.</t>
+  </si>
+  <si>
+    <t>#   The scale is on the row because it belongs to THIS drawing’s paper. Save DXF</t>
+  </si>
+  <si>
+    <t>#   asks nothing at export time.</t>
+  </si>
+  <si>
+    <t>#   The other kind of drawing: not a thing in place seen from somewhere, but a</t>
+  </si>
+  <si>
+    <t>#   part on its own at its standard section, with how many were placed. The</t>
+  </si>
+  <si>
+    <t>#   subject is a definition rather than a position, which is why it is a</t>
+  </si>
+  <si>
+    <t>#   different word. ALL is allowed - asking for forty parts by name is asking for</t>
+  </si>
+  <si>
+    <t>#   the list to go stale.</t>
+  </si>
+  <si>
+    <t># PLOT</t>
+  </si>
+  <si>
+    <t>PART / SECT</t>
+  </si>
+  <si>
+    <t>id / ALL</t>
+  </si>
+  <si>
+    <t>#   PART and SECT are split so each carries its own scale: a gusset and a</t>
+  </si>
+  <si>
+    <t>#   six-metre beam do not share one.</t>
   </si>
   <si>
     <t>END</t>
@@ -1030,7 +1216,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:R154"/>
+  <dimension ref="B1:R212"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="11" customWidth="1"/>
@@ -1476,7 +1662,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B51" s="3" t="s">
         <v>72</v>
       </c>
@@ -1484,719 +1670,1061 @@
         <v>17</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>20</v>
+        <v>73</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>21</v>
+        <v>74</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="52" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B52" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E52" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F52" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G52" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H52" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I52" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B53" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E53" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>29</v>
+        <v>76</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="I51" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B52" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B53" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B54" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B55" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B56" s="2" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="57" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B57" s="1" t="s">
-        <v>73</v>
+      <c r="B57" s="2" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="58" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B58" s="2" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
     </row>
     <row r="59" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B59" s="2" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
     </row>
     <row r="60" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B60" s="2" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
     </row>
     <row r="61" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B61" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="63" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B63" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C63" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="D63" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E63" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F63" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G63" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="H63" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="I63" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="J63" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="K63" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="L63" s="4" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="67" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B67" s="1" t="s">
+    <row r="62" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B62" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="68" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B68" s="2" t="s">
+    <row r="63" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B63" s="2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="69" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B69" s="2" t="s">
+    <row r="67" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B67" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="71" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B71" s="2" t="s">
+      <c r="C67" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G67" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="68" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B68" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G68" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H68" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I68" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="69" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B69" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="73" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B73" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B72" s="3" t="s">
+    <row r="74" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B74" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C72" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D72" s="4" t="s">
+    </row>
+    <row r="75" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B75" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="E72" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="F72" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="G72" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="H72" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="I72" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="J72" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="K72" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="L72" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="M72" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="N72" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="O72" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="P72" s="4" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="76" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B76" s="2" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
     </row>
     <row r="77" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B77" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B79" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="G79" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="H79" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="78" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B78" s="2" t="s">
+      <c r="I79" s="4" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B79" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C79" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D79" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="E79" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="F79" s="4" t="s">
+      <c r="J79" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="G79" s="4" t="s">
+      <c r="K79" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="H79" s="4" t="s">
+      <c r="L79" s="4" t="s">
         <v>107</v>
-      </c>
-      <c r="I79" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="J79" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="K79" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="L79" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="M79" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="N79" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="O79" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="P79" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q79" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="R79" s="4" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="83" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B83" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="84" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B84" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="85" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B85" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="86" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B86" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="87" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B87" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D87" s="4" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="84" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B84" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C84" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D84" s="4" t="s">
+      <c r="E87" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="E84" s="4" t="s">
+      <c r="F87" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G87" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="H87" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="I87" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="J87" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="K87" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="L87" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="M87" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="N87" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="90" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B90" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="F84" s="4" t="s">
+    </row>
+    <row r="91" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B91" s="2" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="87" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B87" s="1" t="s">
+    <row r="92" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B92" s="2" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="88" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B88" s="2" t="s">
+    <row r="93" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B93" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D93" s="4" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="89" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B89" s="2" t="s">
+      <c r="E93" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F93" s="4" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="91" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B91" s="3" t="s">
+    <row r="94" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B94" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="C91" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D91" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="E91" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="F91" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="G91" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="H91" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="I91" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="J91" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="K91" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="92" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B92" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C92" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D92" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="E92" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="F92" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="G92" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="H92" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="I92" s="4" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="93" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B93" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C93" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D93" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="E93" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F93" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="G93" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="H93" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="I93" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="94" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B94" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C94" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D94" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="E94" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="F94" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="G94" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="H94" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="I94" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="J94" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="K94" s="4" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="95" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B95" s="2" t="s">
-        <v>139</v>
+        <v>122</v>
+      </c>
+    </row>
+    <row r="96" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B96" s="2" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="100" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B100" s="1" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
     </row>
     <row r="101" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B101" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="103" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B103" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C103" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="D103" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="E103" s="4" t="s">
-        <v>145</v>
+        <v>125</v>
+      </c>
+    </row>
+    <row r="102" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B102" s="2" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="104" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B104" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="105" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B105" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D105" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E105" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="F105" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G105" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="H105" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="I105" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="J105" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="K105" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="L105" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="M105" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="N105" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="O105" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="P105" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="109" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B109" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="110" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B110" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="111" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B111" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="112" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B112" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D112" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E112" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="F112" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="G112" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="H112" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="I112" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="J112" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="K112" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="L112" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="M112" s="4" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="108" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B108" s="5" t="s">
+      <c r="N112" s="4" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="111" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B111" s="6" t="s">
+      <c r="O112" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="P112" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q112" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="R112" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="116" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B116" s="2" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="112" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B112" s="6"/>
-    </row>
-    <row r="113" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B113" s="6" t="s">
+    <row r="117" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B117" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D117" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="E113" s="7" t="s">
+      <c r="E117" s="4" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="114" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B114" s="6"/>
-      <c r="E114" s="7" t="s">
+      <c r="F117" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="F114" s="7" t="s">
+    </row>
+    <row r="120" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B120" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="G114" s="7" t="s">
+    </row>
+    <row r="121" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B121" s="2" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="115" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B115" s="6"/>
-      <c r="E115" s="7" t="s">
+    <row r="122" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B122" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C122" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D122" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="F115" s="7" t="s">
+      <c r="E122" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="G115" s="7" t="s">
+      <c r="F122" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="G122" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="H122" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="I122" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="J122" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="H115" s="7" t="s">
+      <c r="K122" s="4" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="116" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B116" s="6"/>
-      <c r="E116" s="7" t="s">
+    <row r="125" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B125" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="F116" s="7" t="s">
+    </row>
+    <row r="126" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B126" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="G116" s="7" t="s">
+    </row>
+    <row r="127" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B127" s="2" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="117" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B117" s="6"/>
-      <c r="E117" s="7" t="s">
+    <row r="129" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B129" s="3" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="118" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B118" s="6"/>
-    </row>
-    <row r="119" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B119" s="6" t="s">
+      <c r="C129" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D129" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="E119" s="7" t="s">
+      <c r="E129" s="4" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="120" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B120" s="6"/>
-      <c r="E120" s="7" t="s">
+      <c r="F129" s="4" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="121" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B121" s="6"/>
-    </row>
-    <row r="122" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B122" s="6" t="s">
+      <c r="G129" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="E122" s="7" t="s">
+      <c r="H129" s="4" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="123" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B123" s="6"/>
-      <c r="E123" s="7" t="s">
+      <c r="I129" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="J129" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="K129" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="130" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B130" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C130" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D130" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="E130" s="4" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="124" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B124" s="6"/>
-      <c r="E124" s="7" t="s">
+      <c r="F130" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="G130" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="H130" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="I130" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="131" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B131" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C131" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D131" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="E131" s="4" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="125" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B125" s="6"/>
-      <c r="E125" s="7" t="s">
+      <c r="F131" s="4" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="126" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B126" s="6"/>
-      <c r="E126" s="7" t="s">
+      <c r="G131" s="4" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="127" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B127" s="6"/>
-    </row>
-    <row r="128" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B128" s="6" t="s">
+      <c r="H131" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="E128" s="7" t="s">
+      <c r="I131" s="4" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="129" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B129" s="6"/>
-      <c r="E129" s="7" t="s">
+    <row r="132" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B132" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C132" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D132" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="E132" s="4" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="130" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B130" s="6"/>
-      <c r="E130" s="7" t="s">
+      <c r="F132" s="4" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="131" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B131" s="6"/>
-      <c r="E131" s="7" t="s">
+      <c r="G132" s="4" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="132" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B132" s="6"/>
-      <c r="E132" s="7" t="s">
+      <c r="H132" s="4" t="s">
         <v>176</v>
       </c>
+      <c r="I132" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="J132" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="K132" s="4" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="133" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B133" s="6"/>
-    </row>
-    <row r="134" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B134" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="E134" s="7" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="135" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B135" s="6"/>
-      <c r="E135" s="7" t="s">
+      <c r="B133" s="2" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="136" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B136" s="6"/>
-      <c r="E136" s="7" t="s">
+    <row r="138" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B138" s="1" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="137" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B137" s="6"/>
-    </row>
-    <row r="138" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B138" s="6" t="s">
+    <row r="139" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B139" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="E138" s="7" t="s">
+    </row>
+    <row r="141" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B141" s="3" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="139" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B139" s="6"/>
-    </row>
-    <row r="140" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B140" s="6" t="s">
+      <c r="C141" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="E140" s="7" t="s">
+      <c r="D141" s="4" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="141" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B141" s="6"/>
-      <c r="E141" s="7" t="s">
+      <c r="E141" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="142" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B142" s="6"/>
-      <c r="E142" s="7" t="s">
+      <c r="F141" s="4" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="143" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B143" s="6"/>
-      <c r="E143" s="7" t="s">
+      <c r="G141" s="4" t="s">
         <v>187</v>
       </c>
+      <c r="H141" s="4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="142" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B142" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="143" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B143" s="2" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="144" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B144" s="6"/>
-    </row>
-    <row r="145" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B145" s="6" t="s">
+      <c r="B144" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="145" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B145" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="146" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B146" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="147" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B147" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="148" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B148" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="149" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B149" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="150" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B150" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="151" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B151" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="155" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B155" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="156" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B156" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="157" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B157" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="158" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B158" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="159" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B159" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="160" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B160" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C160" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="D160" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="E160" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="F160" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="E145" s="7" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="146" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B146" s="6"/>
-      <c r="E146" s="7" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="147" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B147" s="6"/>
-    </row>
-    <row r="148" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B148" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="E148" s="7" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="149" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B149" s="6"/>
-    </row>
-    <row r="150" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B150" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="E150" s="7" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="151" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B151" s="6"/>
-      <c r="E151" s="7" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="152" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B152" s="6"/>
-    </row>
-    <row r="153" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B153" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="E153" s="7" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="154" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B154" s="6"/>
-      <c r="E154" s="7" t="s">
-        <v>198</v>
+    </row>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B161" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="162" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B162" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="166" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B166" s="5" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="169" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B169" s="6" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="170" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B170" s="6"/>
+    </row>
+    <row r="171" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B171" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="E171" s="7" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="172" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B172" s="6"/>
+      <c r="E172" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="F172" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="G172" s="7" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="173" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B173" s="6"/>
+      <c r="E173" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="F173" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="G173" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="H173" s="7" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="174" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B174" s="6"/>
+      <c r="E174" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="F174" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="G174" s="7" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="175" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B175" s="6"/>
+      <c r="E175" s="7" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="176" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B176" s="6"/>
+    </row>
+    <row r="177" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B177" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="E177" s="7" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="178" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B178" s="6"/>
+      <c r="E178" s="7" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="179" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B179" s="6"/>
+    </row>
+    <row r="180" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B180" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="E180" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="181" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B181" s="6"/>
+      <c r="E181" s="7" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="182" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B182" s="6"/>
+      <c r="E182" s="7" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="183" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B183" s="6"/>
+      <c r="E183" s="7" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="184" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B184" s="6"/>
+      <c r="E184" s="7" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="185" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B185" s="6"/>
+    </row>
+    <row r="186" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B186" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="E186" s="7" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="187" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B187" s="6"/>
+      <c r="E187" s="7" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="188" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B188" s="6"/>
+      <c r="E188" s="7" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="189" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B189" s="6"/>
+      <c r="E189" s="7" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="190" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B190" s="6"/>
+      <c r="E190" s="7" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="191" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B191" s="6"/>
+    </row>
+    <row r="192" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B192" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="E192" s="7" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="193" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B193" s="6"/>
+      <c r="E193" s="7" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="194" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B194" s="6"/>
+      <c r="E194" s="7" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="195" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B195" s="6"/>
+    </row>
+    <row r="196" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B196" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="E196" s="7" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="197" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B197" s="6"/>
+    </row>
+    <row r="198" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B198" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="E198" s="7" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="199" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B199" s="6"/>
+      <c r="E199" s="7" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="200" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B200" s="6"/>
+      <c r="E200" s="7" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="201" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B201" s="6"/>
+      <c r="E201" s="7" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="202" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B202" s="6"/>
+    </row>
+    <row r="203" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B203" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="E203" s="7" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="204" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B204" s="6"/>
+      <c r="E204" s="7" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="205" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B205" s="6"/>
+    </row>
+    <row r="206" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B206" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="E206" s="7" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="207" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B207" s="6"/>
+    </row>
+    <row r="208" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B208" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="E208" s="7" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="209" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B209" s="6"/>
+      <c r="E209" s="7" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="210" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B210" s="6"/>
+    </row>
+    <row r="211" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B211" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="E211" s="7" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="212" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B212" s="6"/>
+      <c r="E212" s="7" t="s">
+        <v>260</v>
       </c>
     </row>
   </sheetData>
